--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -954,13 +954,13 @@
         <v>-1</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -1008,13 +1008,13 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -1031,13 +1031,13 @@
         <v>-1</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>8</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>9</v>
@@ -1085,13 +1085,13 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -1108,13 +1108,13 @@
         <v>-1</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -1162,13 +1162,13 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>5</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1185,13 +1185,13 @@
         <v>-1</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -1239,13 +1239,13 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1262,13 +1262,13 @@
         <v>-1</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>6</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>9</v>
@@ -1316,13 +1316,13 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1339,13 +1339,13 @@
         <v>-1</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>5</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -1393,13 +1393,13 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>5</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1416,13 +1416,13 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -1470,13 +1470,13 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>5</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1493,13 +1493,13 @@
         <v>-1</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>6</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G11">
         <v>9</v>
@@ -1547,13 +1547,13 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>6</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1570,13 +1570,13 @@
         <v>-1</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -1624,13 +1624,13 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1647,13 +1647,13 @@
         <v>-1</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G13">
         <v>6</v>
@@ -1701,13 +1701,13 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1724,13 +1724,13 @@
         <v>-1</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>9</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>9</v>
@@ -1778,13 +1778,13 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1801,13 +1801,13 @@
         <v>-1</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>6</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -1855,13 +1855,13 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1878,13 +1878,13 @@
         <v>-1</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>6</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>9</v>
@@ -1932,13 +1932,13 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>6</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1955,13 +1955,13 @@
         <v>-1</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -2009,13 +2009,13 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2032,13 +2032,13 @@
         <v>-1</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>10</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>9</v>
@@ -2086,13 +2086,13 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2109,13 +2109,13 @@
         <v>-1</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>8</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>9</v>
@@ -2163,13 +2163,13 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2186,13 +2186,13 @@
         <v>-1</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>5</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G20">
         <v>6</v>
@@ -2240,13 +2240,13 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2263,13 +2263,13 @@
         <v>-1</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>5</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>7</v>
@@ -2317,13 +2317,13 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>5</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2340,13 +2340,13 @@
         <v>-1</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>7</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -2394,13 +2394,13 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2417,13 +2417,13 @@
         <v>-1</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>10</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>10</v>
@@ -2471,13 +2471,13 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2494,13 +2494,13 @@
         <v>-1</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>6</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G24">
         <v>8</v>
@@ -2548,13 +2548,13 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2571,13 +2571,13 @@
         <v>-1</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>5</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G25">
         <v>8</v>
@@ -2625,13 +2625,13 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2648,13 +2648,13 @@
         <v>-1</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>6</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>8</v>
@@ -2702,13 +2702,13 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>6</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2725,13 +2725,13 @@
         <v>-1</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>6</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>6</v>
@@ -2779,13 +2779,13 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>6</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2802,13 +2802,13 @@
         <v>-1</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G28">
         <v>9</v>
@@ -2856,13 +2856,13 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>7</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2879,13 +2879,13 @@
         <v>-1</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E29">
         <v>7</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G29">
         <v>8</v>
@@ -2933,13 +2933,13 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>7</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -2956,13 +2956,13 @@
         <v>-1</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E30">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>10</v>
@@ -3010,13 +3010,13 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3033,13 +3033,13 @@
         <v>-1</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G31">
         <v>10</v>
@@ -3087,13 +3087,13 @@
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3110,13 +3110,13 @@
         <v>-1</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E32">
         <v>7</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3164,13 +3164,13 @@
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>7</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3187,13 +3187,13 @@
         <v>-1</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E33">
         <v>7</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G33">
         <v>7</v>
@@ -3241,13 +3241,13 @@
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>7</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3264,13 +3264,13 @@
         <v>-1</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G34">
         <v>10</v>
@@ -3318,13 +3318,13 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>8</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3341,13 +3341,13 @@
         <v>-1</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E35">
         <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G35">
         <v>10</v>
@@ -3395,13 +3395,13 @@
         <v>-1</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3418,13 +3418,13 @@
         <v>-1</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>6</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -3472,13 +3472,13 @@
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3495,13 +3495,13 @@
         <v>-1</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E37">
         <v>6</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G37">
         <v>8</v>
@@ -3549,13 +3549,13 @@
         <v>-1</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>6</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -3682,13 +3682,13 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>98.2</v>
@@ -3741,13 +3741,13 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>98.2</v>
@@ -3800,13 +3800,13 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>90</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G6">
         <v>98.2</v>
@@ -3859,13 +3859,13 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -3918,13 +3918,13 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -3977,13 +3977,13 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>96.40000000000001</v>
@@ -4036,13 +4036,13 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="E10">
         <v>60</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -4095,13 +4095,13 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -4154,13 +4154,13 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>90.90000000000001</v>
@@ -4213,13 +4213,13 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>80</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G13">
         <v>89.09999999999999</v>
@@ -4272,13 +4272,13 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -4331,13 +4331,13 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>90</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>92.7</v>
@@ -4390,13 +4390,13 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -4449,13 +4449,13 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>70</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G17">
         <v>87.3</v>
@@ -4508,13 +4508,13 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>100</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -4567,13 +4567,13 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -4626,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>96.40000000000001</v>
@@ -4685,13 +4685,13 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>100</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>90.90000000000001</v>
@@ -4744,13 +4744,13 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>70</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G22">
         <v>90.90000000000001</v>
@@ -4803,13 +4803,13 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>100</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -4862,13 +4862,13 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>94.5</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -4980,13 +4980,13 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>98.2</v>
@@ -5039,13 +5039,13 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G27">
         <v>94.5</v>
@@ -5098,13 +5098,13 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>98.2</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>98.2</v>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
@@ -5275,13 +5275,13 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>100</v>
@@ -5334,13 +5334,13 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>100</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>96.40000000000001</v>
@@ -5393,13 +5393,13 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>100</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>89.09999999999999</v>
@@ -5452,13 +5452,13 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>100</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>98.2</v>
@@ -5511,13 +5511,13 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>100</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>100</v>
@@ -5570,13 +5570,13 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>90</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G36">
         <v>85.5</v>
@@ -5629,13 +5629,13 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E37">
         <v>100</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>94.5</v>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -5758,7 +5758,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5767,27 +5767,30 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>73.53</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>26.47</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5796,27 +5799,30 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>8.82</v>
+      </c>
+      <c r="H4">
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5825,19 +5831,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>73.53</v>
+        <v>94.12</v>
       </c>
       <c r="G5">
-        <v>26.47</v>
+        <v>5.88</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5848,7 +5854,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5857,19 +5863,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>91.18000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="G6">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5917,7 +5923,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5958,7 +5964,7 @@
         <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>58</v>
@@ -5966,19 +5972,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920002</v>
+        <v>22330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>58</v>
@@ -5986,16 +5992,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920002</v>
+        <v>22330051920004</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6006,19 +6012,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920003</v>
+        <v>22330051920001</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>58</v>
@@ -6026,19 +6032,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920003</v>
+        <v>22330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
@@ -6046,16 +6052,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920003</v>
+        <v>22330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -6066,19 +6072,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920004</v>
+        <v>22330051920009</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
@@ -6086,19 +6092,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920004</v>
+        <v>22330051920010</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
@@ -6106,16 +6112,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920004</v>
+        <v>22330051920011</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6126,19 +6132,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920001</v>
+        <v>22330051920007</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>58</v>
@@ -6146,19 +6152,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920001</v>
+        <v>22330051920013</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>58</v>
@@ -6166,16 +6172,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920001</v>
+        <v>22330051920014</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -6186,19 +6192,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920005</v>
+        <v>22330051920015</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>58</v>
@@ -6206,19 +6212,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920005</v>
+        <v>22330051920016</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>58</v>
@@ -6226,16 +6232,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920005</v>
+        <v>22330051920320</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6246,19 +6252,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920006</v>
+        <v>22330051920017</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
         <v>58</v>
@@ -6266,19 +6272,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920006</v>
+        <v>22330051920018</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>58</v>
@@ -6286,16 +6292,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920006</v>
+        <v>22330051920321</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -6306,19 +6312,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920009</v>
+        <v>22330051920012</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>58</v>
@@ -6326,19 +6332,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920009</v>
+        <v>22330051920020</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
         <v>58</v>
@@ -6346,16 +6352,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920009</v>
+        <v>22330051920382</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -6366,19 +6372,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920010</v>
+        <v>22330051920021</v>
       </c>
       <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
         <v>70</v>
       </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
         <v>58</v>
@@ -6386,19 +6392,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920010</v>
+        <v>22330051920022</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>58</v>
@@ -6406,16 +6412,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920010</v>
+        <v>22330051920322</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -6426,19 +6432,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920011</v>
+        <v>22330051920023</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
         <v>58</v>
@@ -6446,19 +6452,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920011</v>
+        <v>22330051920024</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
         <v>58</v>
@@ -6466,16 +6472,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920011</v>
+        <v>22330051920025</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -6486,19 +6492,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920007</v>
+        <v>22330051920326</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>58</v>
@@ -6506,19 +6512,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920007</v>
+        <v>22330051920026</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
         <v>58</v>
@@ -6526,16 +6532,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>22330051920007</v>
+        <v>22330051920173</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s">
         <v>6</v>
@@ -6546,19 +6552,19 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>22330051920013</v>
+        <v>22330051920330</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
         <v>58</v>
@@ -6566,19 +6572,19 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>22330051920013</v>
+        <v>22330051920027</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
         <v>58</v>
@@ -6586,16 +6592,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>22330051920013</v>
+        <v>22330051920028</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
@@ -6606,1381 +6612,21 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>22330051920014</v>
+        <v>22330051920332</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920014</v>
-      </c>
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" t="s">
-        <v>125</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920014</v>
-      </c>
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" t="s">
-        <v>125</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920015</v>
-      </c>
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920015</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>100</v>
-      </c>
-      <c r="D39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920015</v>
-      </c>
-      <c r="B40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" t="s">
-        <v>100</v>
-      </c>
-      <c r="D40" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920016</v>
-      </c>
-      <c r="B41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" t="s">
-        <v>127</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920016</v>
-      </c>
-      <c r="B42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920016</v>
-      </c>
-      <c r="B43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" t="s">
-        <v>101</v>
-      </c>
-      <c r="D43" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920320</v>
-      </c>
-      <c r="B44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" t="s">
-        <v>102</v>
-      </c>
-      <c r="D44" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920320</v>
-      </c>
-      <c r="B45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920320</v>
-      </c>
-      <c r="B46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920017</v>
-      </c>
-      <c r="B47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" t="s">
-        <v>103</v>
-      </c>
-      <c r="D47" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>22330051920017</v>
-      </c>
-      <c r="B48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" t="s">
-        <v>103</v>
-      </c>
-      <c r="D48" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>22330051920017</v>
-      </c>
-      <c r="B49" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" t="s">
-        <v>129</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920018</v>
-      </c>
-      <c r="B50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" t="s">
-        <v>130</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920018</v>
-      </c>
-      <c r="B51" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" t="s">
-        <v>130</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920018</v>
-      </c>
-      <c r="B52" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920321</v>
-      </c>
-      <c r="B53" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53" t="s">
-        <v>105</v>
-      </c>
-      <c r="D53" t="s">
-        <v>131</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920321</v>
-      </c>
-      <c r="B54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" t="s">
-        <v>131</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920321</v>
-      </c>
-      <c r="B55" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" t="s">
-        <v>131</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920012</v>
-      </c>
-      <c r="B56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" t="s">
-        <v>87</v>
-      </c>
-      <c r="D56" t="s">
-        <v>132</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920012</v>
-      </c>
-      <c r="B57" t="s">
-        <v>78</v>
-      </c>
-      <c r="C57" t="s">
-        <v>87</v>
-      </c>
-      <c r="D57" t="s">
-        <v>132</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920012</v>
-      </c>
-      <c r="B58" t="s">
-        <v>78</v>
-      </c>
-      <c r="C58" t="s">
-        <v>87</v>
-      </c>
-      <c r="D58" t="s">
-        <v>132</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22330051920020</v>
-      </c>
-      <c r="B59" t="s">
-        <v>79</v>
-      </c>
-      <c r="C59" t="s">
-        <v>106</v>
-      </c>
-      <c r="D59" t="s">
-        <v>133</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22330051920020</v>
-      </c>
-      <c r="B60" t="s">
-        <v>79</v>
-      </c>
-      <c r="C60" t="s">
-        <v>106</v>
-      </c>
-      <c r="D60" t="s">
-        <v>133</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22330051920020</v>
-      </c>
-      <c r="B61" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" t="s">
-        <v>106</v>
-      </c>
-      <c r="D61" t="s">
-        <v>133</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920382</v>
-      </c>
-      <c r="B62" t="s">
-        <v>79</v>
-      </c>
-      <c r="C62" t="s">
-        <v>107</v>
-      </c>
-      <c r="D62" t="s">
-        <v>134</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920382</v>
-      </c>
-      <c r="B63" t="s">
-        <v>79</v>
-      </c>
-      <c r="C63" t="s">
-        <v>107</v>
-      </c>
-      <c r="D63" t="s">
-        <v>134</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330051920382</v>
-      </c>
-      <c r="B64" t="s">
-        <v>79</v>
-      </c>
-      <c r="C64" t="s">
-        <v>107</v>
-      </c>
-      <c r="D64" t="s">
-        <v>134</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330051920021</v>
-      </c>
-      <c r="B65" t="s">
-        <v>80</v>
-      </c>
-      <c r="C65" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920021</v>
-      </c>
-      <c r="B66" t="s">
-        <v>80</v>
-      </c>
-      <c r="C66" t="s">
-        <v>70</v>
-      </c>
-      <c r="D66" t="s">
-        <v>135</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920021</v>
-      </c>
-      <c r="B67" t="s">
-        <v>80</v>
-      </c>
-      <c r="C67" t="s">
-        <v>70</v>
-      </c>
-      <c r="D67" t="s">
-        <v>135</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>22330051920022</v>
-      </c>
-      <c r="B68" t="s">
-        <v>81</v>
-      </c>
-      <c r="C68" t="s">
-        <v>87</v>
-      </c>
-      <c r="D68" t="s">
-        <v>136</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>22330051920022</v>
-      </c>
-      <c r="B69" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" t="s">
-        <v>87</v>
-      </c>
-      <c r="D69" t="s">
-        <v>136</v>
-      </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>22330051920022</v>
-      </c>
-      <c r="B70" t="s">
-        <v>81</v>
-      </c>
-      <c r="C70" t="s">
-        <v>87</v>
-      </c>
-      <c r="D70" t="s">
-        <v>136</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>22330051920322</v>
-      </c>
-      <c r="B71" t="s">
-        <v>82</v>
-      </c>
-      <c r="C71" t="s">
-        <v>108</v>
-      </c>
-      <c r="D71" t="s">
-        <v>137</v>
-      </c>
-      <c r="E71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>22330051920322</v>
-      </c>
-      <c r="B72" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" t="s">
-        <v>108</v>
-      </c>
-      <c r="D72" t="s">
-        <v>137</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>22330051920322</v>
-      </c>
-      <c r="B73" t="s">
-        <v>82</v>
-      </c>
-      <c r="C73" t="s">
-        <v>108</v>
-      </c>
-      <c r="D73" t="s">
-        <v>137</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>22330051920023</v>
-      </c>
-      <c r="B74" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" t="s">
-        <v>109</v>
-      </c>
-      <c r="D74" t="s">
-        <v>138</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>22330051920023</v>
-      </c>
-      <c r="B75" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" t="s">
-        <v>109</v>
-      </c>
-      <c r="D75" t="s">
-        <v>138</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>22330051920023</v>
-      </c>
-      <c r="B76" t="s">
-        <v>83</v>
-      </c>
-      <c r="C76" t="s">
-        <v>109</v>
-      </c>
-      <c r="D76" t="s">
-        <v>138</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>22330051920024</v>
-      </c>
-      <c r="B77" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" t="s">
-        <v>95</v>
-      </c>
-      <c r="D77" t="s">
-        <v>139</v>
-      </c>
-      <c r="E77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>22330051920024</v>
-      </c>
-      <c r="B78" t="s">
-        <v>84</v>
-      </c>
-      <c r="C78" t="s">
-        <v>95</v>
-      </c>
-      <c r="D78" t="s">
-        <v>139</v>
-      </c>
-      <c r="E78" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>22330051920024</v>
-      </c>
-      <c r="B79" t="s">
-        <v>84</v>
-      </c>
-      <c r="C79" t="s">
-        <v>95</v>
-      </c>
-      <c r="D79" t="s">
-        <v>139</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>22330051920025</v>
-      </c>
-      <c r="B80" t="s">
-        <v>85</v>
-      </c>
-      <c r="C80" t="s">
-        <v>110</v>
-      </c>
-      <c r="D80" t="s">
-        <v>140</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>22330051920025</v>
-      </c>
-      <c r="B81" t="s">
-        <v>85</v>
-      </c>
-      <c r="C81" t="s">
-        <v>110</v>
-      </c>
-      <c r="D81" t="s">
-        <v>140</v>
-      </c>
-      <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>22330051920025</v>
-      </c>
-      <c r="B82" t="s">
-        <v>85</v>
-      </c>
-      <c r="C82" t="s">
-        <v>110</v>
-      </c>
-      <c r="D82" t="s">
-        <v>140</v>
-      </c>
-      <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>22330051920326</v>
-      </c>
-      <c r="B83" t="s">
-        <v>86</v>
-      </c>
-      <c r="C83" t="s">
-        <v>111</v>
-      </c>
-      <c r="D83" t="s">
-        <v>141</v>
-      </c>
-      <c r="E83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>22330051920326</v>
-      </c>
-      <c r="B84" t="s">
-        <v>86</v>
-      </c>
-      <c r="C84" t="s">
-        <v>111</v>
-      </c>
-      <c r="D84" t="s">
-        <v>141</v>
-      </c>
-      <c r="E84" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>22330051920326</v>
-      </c>
-      <c r="B85" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" t="s">
-        <v>111</v>
-      </c>
-      <c r="D85" t="s">
-        <v>141</v>
-      </c>
-      <c r="E85" t="s">
-        <v>6</v>
-      </c>
-      <c r="F85" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>22330051920026</v>
-      </c>
-      <c r="B86" t="s">
-        <v>86</v>
-      </c>
-      <c r="C86" t="s">
-        <v>112</v>
-      </c>
-      <c r="D86" t="s">
-        <v>142</v>
-      </c>
-      <c r="E86" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>22330051920026</v>
-      </c>
-      <c r="B87" t="s">
-        <v>86</v>
-      </c>
-      <c r="C87" t="s">
-        <v>112</v>
-      </c>
-      <c r="D87" t="s">
-        <v>142</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>22330051920026</v>
-      </c>
-      <c r="B88" t="s">
-        <v>86</v>
-      </c>
-      <c r="C88" t="s">
-        <v>112</v>
-      </c>
-      <c r="D88" t="s">
-        <v>142</v>
-      </c>
-      <c r="E88" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>22330051920173</v>
-      </c>
-      <c r="B89" t="s">
-        <v>86</v>
-      </c>
-      <c r="C89" t="s">
-        <v>84</v>
-      </c>
-      <c r="D89" t="s">
-        <v>143</v>
-      </c>
-      <c r="E89" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>22330051920173</v>
-      </c>
-      <c r="B90" t="s">
-        <v>86</v>
-      </c>
-      <c r="C90" t="s">
-        <v>84</v>
-      </c>
-      <c r="D90" t="s">
-        <v>143</v>
-      </c>
-      <c r="E90" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>22330051920173</v>
-      </c>
-      <c r="B91" t="s">
-        <v>86</v>
-      </c>
-      <c r="C91" t="s">
-        <v>84</v>
-      </c>
-      <c r="D91" t="s">
-        <v>143</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>22330051920330</v>
-      </c>
-      <c r="B92" t="s">
-        <v>86</v>
-      </c>
-      <c r="C92" t="s">
-        <v>87</v>
-      </c>
-      <c r="D92" t="s">
-        <v>144</v>
-      </c>
-      <c r="E92" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>22330051920330</v>
-      </c>
-      <c r="B93" t="s">
-        <v>86</v>
-      </c>
-      <c r="C93" t="s">
-        <v>87</v>
-      </c>
-      <c r="D93" t="s">
-        <v>144</v>
-      </c>
-      <c r="E93" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>22330051920330</v>
-      </c>
-      <c r="B94" t="s">
-        <v>86</v>
-      </c>
-      <c r="C94" t="s">
-        <v>87</v>
-      </c>
-      <c r="D94" t="s">
-        <v>144</v>
-      </c>
-      <c r="E94" t="s">
-        <v>6</v>
-      </c>
-      <c r="F94" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>22330051920027</v>
-      </c>
-      <c r="B95" t="s">
-        <v>87</v>
-      </c>
-      <c r="C95" t="s">
-        <v>113</v>
-      </c>
-      <c r="D95" t="s">
-        <v>145</v>
-      </c>
-      <c r="E95" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>22330051920027</v>
-      </c>
-      <c r="B96" t="s">
-        <v>87</v>
-      </c>
-      <c r="C96" t="s">
-        <v>113</v>
-      </c>
-      <c r="D96" t="s">
-        <v>145</v>
-      </c>
-      <c r="E96" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>22330051920027</v>
-      </c>
-      <c r="B97" t="s">
-        <v>87</v>
-      </c>
-      <c r="C97" t="s">
-        <v>113</v>
-      </c>
-      <c r="D97" t="s">
-        <v>145</v>
-      </c>
-      <c r="E97" t="s">
-        <v>6</v>
-      </c>
-      <c r="F97" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>22330051920028</v>
-      </c>
-      <c r="B98" t="s">
-        <v>88</v>
-      </c>
-      <c r="C98" t="s">
-        <v>114</v>
-      </c>
-      <c r="D98" t="s">
-        <v>146</v>
-      </c>
-      <c r="E98" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>22330051920028</v>
-      </c>
-      <c r="B99" t="s">
-        <v>88</v>
-      </c>
-      <c r="C99" t="s">
-        <v>114</v>
-      </c>
-      <c r="D99" t="s">
-        <v>146</v>
-      </c>
-      <c r="E99" t="s">
-        <v>7</v>
-      </c>
-      <c r="F99" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>22330051920028</v>
-      </c>
-      <c r="B100" t="s">
-        <v>88</v>
-      </c>
-      <c r="C100" t="s">
-        <v>114</v>
-      </c>
-      <c r="D100" t="s">
-        <v>146</v>
-      </c>
-      <c r="E100" t="s">
-        <v>6</v>
-      </c>
-      <c r="F100" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>22330051920332</v>
-      </c>
-      <c r="B101" t="s">
-        <v>89</v>
-      </c>
-      <c r="C101" t="s">
-        <v>79</v>
-      </c>
-      <c r="D101" t="s">
-        <v>147</v>
-      </c>
-      <c r="E101" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>22330051920332</v>
-      </c>
-      <c r="B102" t="s">
-        <v>89</v>
-      </c>
-      <c r="C102" t="s">
-        <v>79</v>
-      </c>
-      <c r="D102" t="s">
-        <v>147</v>
-      </c>
-      <c r="E102" t="s">
-        <v>7</v>
-      </c>
-      <c r="F102" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>22330051920332</v>
-      </c>
-      <c r="B103" t="s">
-        <v>89</v>
-      </c>
-      <c r="C103" t="s">
-        <v>79</v>
-      </c>
-      <c r="D103" t="s">
-        <v>147</v>
-      </c>
-      <c r="E103" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" t="s">
         <v>58</v>
       </c>
     </row>
@@ -8029,7 +6675,7 @@
         <v>115</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8046,7 +6692,7 @@
         <v>116</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8063,7 +6709,7 @@
         <v>99</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8080,7 +6726,7 @@
         <v>117</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8097,7 +6743,7 @@
         <v>118</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8114,7 +6760,7 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8131,7 +6777,7 @@
         <v>120</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8148,7 +6794,7 @@
         <v>121</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8165,7 +6811,7 @@
         <v>122</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8182,7 +6828,7 @@
         <v>123</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8199,7 +6845,7 @@
         <v>124</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8216,7 +6862,7 @@
         <v>125</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8233,7 +6879,7 @@
         <v>126</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8250,7 +6896,7 @@
         <v>127</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8267,7 +6913,7 @@
         <v>128</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8284,7 +6930,7 @@
         <v>129</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8301,7 +6947,7 @@
         <v>130</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8318,7 +6964,7 @@
         <v>131</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8335,7 +6981,7 @@
         <v>132</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8352,7 +6998,7 @@
         <v>133</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8369,7 +7015,7 @@
         <v>134</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8386,7 +7032,7 @@
         <v>135</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8403,7 +7049,7 @@
         <v>136</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8420,7 +7066,7 @@
         <v>137</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8437,7 +7083,7 @@
         <v>138</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8454,7 +7100,7 @@
         <v>139</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8471,7 +7117,7 @@
         <v>140</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8488,7 +7134,7 @@
         <v>141</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8505,7 +7151,7 @@
         <v>142</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8522,7 +7168,7 @@
         <v>143</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8539,7 +7185,7 @@
         <v>144</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8556,7 +7202,7 @@
         <v>145</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8573,7 +7219,7 @@
         <v>146</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8590,7 +7236,7 @@
         <v>147</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8600,7 +7246,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8630,6 +7276,857 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920003</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920003</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920006</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920006</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920011</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920011</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920017</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920017</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920018</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920018</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920321</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920321</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920021</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920021</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920002</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920004</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920001</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920005</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920009</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920013</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920014</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920016</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920320</v>
+      </c>
+      <c r="B24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920012</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920020</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920382</v>
+      </c>
+      <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920022</v>
+      </c>
+      <c r="B28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920322</v>
+      </c>
+      <c r="B29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920023</v>
+      </c>
+      <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>22330051920024</v>
+      </c>
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>22330051920025</v>
+      </c>
+      <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>22330051920326</v>
+      </c>
+      <c r="B33" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>22330051920026</v>
+      </c>
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>22330051920173</v>
+      </c>
+      <c r="B35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>22330051920330</v>
+      </c>
+      <c r="B36" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>22330051920027</v>
+      </c>
+      <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>22330051920332</v>
+      </c>
+      <c r="B38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -951,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -1005,7 +1005,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -1028,7 +1028,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -1082,7 +1082,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -1105,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -1159,7 +1159,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -1236,7 +1236,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1259,7 +1259,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -1313,7 +1313,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -1336,7 +1336,7 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -1390,7 +1390,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1413,7 +1413,7 @@
         <v>4</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1467,7 +1467,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -1490,7 +1490,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>9</v>
@@ -1544,7 +1544,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1567,7 +1567,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1621,7 +1621,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1644,7 +1644,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -1698,7 +1698,7 @@
         <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1721,7 +1721,7 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -1775,7 +1775,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1798,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -1852,7 +1852,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1875,7 +1875,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1929,7 +1929,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -1952,7 +1952,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -2006,7 +2006,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2029,7 +2029,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -2083,7 +2083,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -2106,7 +2106,7 @@
         <v>10</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -2183,7 +2183,7 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2237,7 +2237,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2260,7 +2260,7 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2314,7 +2314,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -2337,7 +2337,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -2391,7 +2391,7 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -2414,7 +2414,7 @@
         <v>10</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D23">
         <v>10</v>
@@ -2468,7 +2468,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2491,7 +2491,7 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>7</v>
@@ -2545,7 +2545,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2568,7 +2568,7 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -2622,7 +2622,7 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -2645,7 +2645,7 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -2699,7 +2699,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -2722,7 +2722,7 @@
         <v>9</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -2776,7 +2776,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2799,7 +2799,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>9</v>
@@ -2853,7 +2853,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -2876,7 +2876,7 @@
         <v>10</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2930,7 +2930,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2953,7 +2953,7 @@
         <v>10</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>10</v>
@@ -3007,7 +3007,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -3084,7 +3084,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3107,7 +3107,7 @@
         <v>9</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>9</v>
@@ -3161,7 +3161,7 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>9</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>9</v>
@@ -3238,7 +3238,7 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3261,7 +3261,7 @@
         <v>10</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D34">
         <v>10</v>
@@ -3315,7 +3315,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -3338,7 +3338,7 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>10</v>
@@ -3392,7 +3392,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3415,7 +3415,7 @@
         <v>4</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -3469,7 +3469,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3492,7 +3492,7 @@
         <v>9</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>7</v>
@@ -3546,7 +3546,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -3679,7 +3679,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -3738,7 +3738,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -3797,7 +3797,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -3856,7 +3856,7 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -3915,7 +3915,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -3974,7 +3974,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -4033,7 +4033,7 @@
         <v>83.3</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D10">
         <v>86.7</v>
@@ -4092,7 +4092,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -4151,7 +4151,7 @@
         <v>93.3</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -4210,7 +4210,7 @@
         <v>93.3</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -4269,7 +4269,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -4328,7 +4328,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -4387,7 +4387,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -4446,7 +4446,7 @@
         <v>93.3</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -4505,7 +4505,7 @@
         <v>96.7</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -4564,7 +4564,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -4623,7 +4623,7 @@
         <v>96.7</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -4682,7 +4682,7 @@
         <v>96.7</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -4741,7 +4741,7 @@
         <v>93.3</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -4800,7 +4800,7 @@
         <v>93.3</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -4859,7 +4859,7 @@
         <v>96.7</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -4918,7 +4918,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -4977,7 +4977,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -5036,7 +5036,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -5095,7 +5095,7 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -5154,7 +5154,7 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -5213,7 +5213,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -5272,7 +5272,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -5331,7 +5331,7 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -5390,7 +5390,7 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D33">
         <v>100</v>
@@ -5449,7 +5449,7 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -5508,7 +5508,7 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -5567,7 +5567,7 @@
         <v>80</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -5626,7 +5626,7 @@
         <v>100</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -5738,27 +5738,30 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>73.53</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>26.47</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
       <c r="I2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5767,19 +5770,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>73.53</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G3">
-        <v>26.47</v>
+        <v>11.76</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5923,7 +5926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5948,686 +5951,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920002</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920003</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920004</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920001</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920009</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920010</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920011</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920007</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920013</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920014</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920015</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920016</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920320</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920017</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920018</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920321</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920012</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920020</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920382</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920021</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920022</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920322</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920023</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920024</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920025</v>
-      </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920326</v>
-      </c>
-      <c r="B29" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920026</v>
-      </c>
-      <c r="B30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" t="s">
-        <v>142</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920173</v>
-      </c>
-      <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>143</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920330</v>
-      </c>
-      <c r="B32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" t="s">
-        <v>144</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920027</v>
-      </c>
-      <c r="B33" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" t="s">
-        <v>145</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920028</v>
-      </c>
-      <c r="B34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" t="s">
-        <v>146</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920332</v>
-      </c>
-      <c r="B35" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -6675,7 +5998,7 @@
         <v>115</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6692,7 +6015,7 @@
         <v>116</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6709,7 +6032,7 @@
         <v>99</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6726,7 +6049,7 @@
         <v>117</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6743,7 +6066,7 @@
         <v>118</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6760,7 +6083,7 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6777,7 +6100,7 @@
         <v>120</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6794,7 +6117,7 @@
         <v>121</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6811,7 +6134,7 @@
         <v>122</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6828,7 +6151,7 @@
         <v>123</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6845,7 +6168,7 @@
         <v>124</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6862,7 +6185,7 @@
         <v>125</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6879,7 +6202,7 @@
         <v>126</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6896,7 +6219,7 @@
         <v>127</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6913,7 +6236,7 @@
         <v>128</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6930,7 +6253,7 @@
         <v>129</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6947,7 +6270,7 @@
         <v>130</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6964,7 +6287,7 @@
         <v>131</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6981,7 +6304,7 @@
         <v>132</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6998,7 +6321,7 @@
         <v>133</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7015,7 +6338,7 @@
         <v>134</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7032,7 +6355,7 @@
         <v>135</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7049,7 +6372,7 @@
         <v>136</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7066,7 +6389,7 @@
         <v>137</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7083,7 +6406,7 @@
         <v>138</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7100,7 +6423,7 @@
         <v>139</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7117,7 +6440,7 @@
         <v>140</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7134,7 +6457,7 @@
         <v>141</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7151,7 +6474,7 @@
         <v>142</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7168,7 +6491,7 @@
         <v>143</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7185,7 +6508,7 @@
         <v>144</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7202,7 +6525,7 @@
         <v>145</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7219,7 +6542,7 @@
         <v>146</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7236,7 +6559,7 @@
         <v>147</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7246,7 +6569,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7278,39 +6601,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920003</v>
+        <v>22330051920007</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>58</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920003</v>
+        <v>22330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7324,16 +6647,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920006</v>
+        <v>22330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7342,24 +6665,24 @@
         <v>58</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920006</v>
+        <v>22330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>58</v>
@@ -7370,39 +6693,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920011</v>
+        <v>22330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920011</v>
+        <v>22330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -7416,25 +6739,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920017</v>
+        <v>22330051920011</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -7474,27 +6797,27 @@
         <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920018</v>
+        <v>22330051920021</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -7504,627 +6827,6 @@
       </c>
       <c r="G11">
         <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920321</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920321</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" t="s">
-        <v>131</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920021</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920021</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920002</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920004</v>
-      </c>
-      <c r="B17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920001</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920005</v>
-      </c>
-      <c r="B19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920009</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920013</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920014</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920016</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920320</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920012</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920020</v>
-      </c>
-      <c r="B26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920382</v>
-      </c>
-      <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920022</v>
-      </c>
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920322</v>
-      </c>
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920023</v>
-      </c>
-      <c r="B30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920024</v>
-      </c>
-      <c r="B31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920025</v>
-      </c>
-      <c r="B32" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" t="s">
-        <v>110</v>
-      </c>
-      <c r="D32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920326</v>
-      </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920026</v>
-      </c>
-      <c r="B34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" t="s">
-        <v>142</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>58</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920173</v>
-      </c>
-      <c r="B35" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35" t="s">
-        <v>143</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920330</v>
-      </c>
-      <c r="B36" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" t="s">
-        <v>144</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920027</v>
-      </c>
-      <c r="B37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" t="s">
-        <v>145</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>22330051920332</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" t="s">
-        <v>147</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="153">
   <si>
     <t>Materia</t>
   </si>
@@ -195,7 +195,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Hernández Contreras Ángel</t>
   </si>
   <si>
     <t>NC</t>
@@ -5764,7 +5779,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3">
         <v>34</v>
@@ -5796,7 +5811,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>34</v>
@@ -5828,7 +5843,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>34</v>
@@ -5860,7 +5875,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>34</v>
@@ -5892,7 +5907,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>34</v>
@@ -5935,16 +5950,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5969,16 +5984,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>56</v>
@@ -5989,13 +6004,13 @@
         <v>22330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6006,13 +6021,13 @@
         <v>22330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6023,13 +6038,13 @@
         <v>22330051920004</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6040,13 +6055,13 @@
         <v>22330051920001</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6057,13 +6072,13 @@
         <v>22330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6074,13 +6089,13 @@
         <v>22330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6091,13 +6106,13 @@
         <v>22330051920009</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6108,13 +6123,13 @@
         <v>22330051920010</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6125,13 +6140,13 @@
         <v>22330051920011</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6142,13 +6157,13 @@
         <v>22330051920007</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6159,13 +6174,13 @@
         <v>22330051920013</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6176,13 +6191,13 @@
         <v>22330051920014</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6193,13 +6208,13 @@
         <v>22330051920015</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6210,13 +6225,13 @@
         <v>22330051920016</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6227,13 +6242,13 @@
         <v>22330051920320</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6244,13 +6259,13 @@
         <v>22330051920017</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6261,13 +6276,13 @@
         <v>22330051920018</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6278,13 +6293,13 @@
         <v>22330051920321</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6295,13 +6310,13 @@
         <v>22330051920012</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6312,13 +6327,13 @@
         <v>22330051920020</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6329,13 +6344,13 @@
         <v>22330051920382</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6346,13 +6361,13 @@
         <v>22330051920021</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6363,13 +6378,13 @@
         <v>22330051920022</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6380,13 +6395,13 @@
         <v>22330051920322</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6397,13 +6412,13 @@
         <v>22330051920023</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6414,13 +6429,13 @@
         <v>22330051920024</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6431,13 +6446,13 @@
         <v>22330051920025</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6448,13 +6463,13 @@
         <v>22330051920326</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6465,13 +6480,13 @@
         <v>22330051920026</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6482,13 +6497,13 @@
         <v>22330051920173</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6499,13 +6514,13 @@
         <v>22330051920330</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6516,13 +6531,13 @@
         <v>22330051920027</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6533,13 +6548,13 @@
         <v>22330051920028</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6550,13 +6565,13 @@
         <v>22330051920332</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D35" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6578,16 +6593,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6604,19 +6619,19 @@
         <v>22330051920007</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6627,13 +6642,13 @@
         <v>22330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6650,19 +6665,19 @@
         <v>22330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6673,19 +6688,19 @@
         <v>22330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6696,13 +6711,13 @@
         <v>22330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6719,13 +6734,13 @@
         <v>22330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -6742,13 +6757,13 @@
         <v>22330051920011</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -6765,13 +6780,13 @@
         <v>22330051920017</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -6788,13 +6803,13 @@
         <v>22330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -6811,13 +6826,13 @@
         <v>22330051920021</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>

--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -198,12 +197,12 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
@@ -225,265 +224,82 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>ARGUELLES</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
+    <t>ROCETE</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>JERONIMO</t>
   </si>
   <si>
     <t>AVELINO</t>
   </si>
   <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>RUBEN DE JESUS</t>
+    <t>ANGELO</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
   </si>
   <si>
     <t>DANIEL</t>
   </si>
   <si>
-    <t>CHRISTOPHER</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
     <t>EDER</t>
   </si>
   <si>
-    <t>LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>ISABEL</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>JESUS YAEL</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
     <t>LUIS</t>
   </si>
   <si>
     <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>VALENTINA</t>
-  </si>
-  <si>
-    <t>DYLAN OSMAR</t>
-  </si>
-  <si>
-    <t>GABRIEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>SAUL AZAEL</t>
-  </si>
-  <si>
-    <t>ANGEL GUILLERMO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>ISAAC JOHAMET</t>
-  </si>
-  <si>
-    <t>EIDAN JOSEPH</t>
-  </si>
-  <si>
-    <t>CHRISTOPHER ANDRUS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -536,11 +352,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -981,7 +798,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1058,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1135,7 +952,7 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1171,7 +988,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1212,7 +1029,7 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1289,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1366,7 +1183,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1402,7 +1219,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1443,7 +1260,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1520,7 +1337,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1597,7 +1414,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1674,7 +1491,7 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1710,7 +1527,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1751,7 +1568,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1828,7 +1645,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1905,7 +1722,7 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1982,7 +1799,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2018,7 +1835,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -2059,7 +1876,7 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2136,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2213,7 +2030,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2249,7 +2066,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2290,7 +2107,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2367,7 +2184,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2403,7 +2220,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2444,7 +2261,7 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2521,7 +2338,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2557,7 +2374,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2598,7 +2415,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2634,7 +2451,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -2675,7 +2492,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2711,7 +2528,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2752,7 +2569,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2788,7 +2605,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2829,7 +2646,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2906,7 +2723,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2983,7 +2800,7 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3060,7 +2877,7 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3137,7 +2954,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3173,7 +2990,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -3214,7 +3031,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3291,7 +3108,7 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3368,7 +3185,7 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3445,7 +3262,7 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3522,7 +3339,7 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3709,7 +3526,7 @@
         <v>98.2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3768,7 +3585,7 @@
         <v>98.2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3827,7 +3644,7 @@
         <v>98.2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3886,7 +3703,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3945,7 +3762,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4004,7 +3821,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4063,7 +3880,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4122,7 +3939,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4181,7 +3998,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4240,7 +4057,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4299,7 +4116,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4358,7 +4175,7 @@
         <v>92.7</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -4417,7 +4234,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -4476,7 +4293,7 @@
         <v>87.3</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4535,7 +4352,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4594,7 +4411,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -4653,7 +4470,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -4712,7 +4529,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -4771,7 +4588,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -4830,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4889,7 +4706,7 @@
         <v>94.5</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4948,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5007,7 +4824,7 @@
         <v>98.2</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5066,7 +4883,7 @@
         <v>94.5</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5125,7 +4942,7 @@
         <v>98.2</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5184,7 +5001,7 @@
         <v>98.2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5243,7 +5060,7 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5302,7 +5119,7 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5361,7 +5178,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5420,7 +5237,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5479,7 +5296,7 @@
         <v>98.2</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5538,7 +5355,7 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -5597,7 +5414,7 @@
         <v>85.5</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -5656,7 +5473,7 @@
         <v>94.5</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -5708,6 +5525,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5758,11 +5577,11 @@
       <c r="E2">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>73.53</v>
-      </c>
-      <c r="G2">
-        <v>26.47</v>
+      <c r="F2" s="2">
+        <v>73.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>26.5</v>
       </c>
       <c r="H2">
         <v>6.9</v>
@@ -5770,13 +5589,13 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5785,30 +5604,30 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>88.23999999999999</v>
-      </c>
-      <c r="G3">
-        <v>11.76</v>
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>85.3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>14.7</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -5817,24 +5636,24 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>91.18000000000001</v>
-      </c>
-      <c r="G4">
-        <v>8.82</v>
+        <v>4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>88.2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>11.8</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5854,11 +5673,11 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5">
-        <v>94.12</v>
-      </c>
-      <c r="G5">
-        <v>5.88</v>
+      <c r="F5" s="2">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5.9</v>
       </c>
       <c r="H5">
         <v>8.1</v>
@@ -5866,7 +5685,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5886,11 +5705,11 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6">
-        <v>94.12</v>
-      </c>
-      <c r="G6">
-        <v>5.88</v>
+      <c r="F6" s="2">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5.9</v>
       </c>
       <c r="H6">
         <v>7.8</v>
@@ -5898,7 +5717,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5918,11 +5737,11 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7">
-        <v>94.12</v>
-      </c>
-      <c r="G7">
-        <v>5.88</v>
+      <c r="F7" s="2">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5.9</v>
       </c>
       <c r="H7">
         <v>8.1</v>
@@ -5930,7 +5749,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5975,616 +5794,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22330051920002</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920003</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920004</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920001</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920009</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920010</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920011</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920007</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920013</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920014</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920015</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920016</v>
-      </c>
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920320</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" t="s">
-        <v>133</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920017</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" t="s">
-        <v>134</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920018</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920321</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920012</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920020</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920382</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" t="s">
-        <v>139</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920021</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" t="s">
-        <v>140</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920022</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920322</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" t="s">
-        <v>142</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920023</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920024</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920025</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" t="s">
-        <v>145</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920326</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" t="s">
-        <v>146</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920026</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" t="s">
-        <v>147</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920173</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" t="s">
-        <v>148</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920330</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" t="s">
-        <v>149</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920027</v>
-      </c>
-      <c r="B33" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" t="s">
-        <v>118</v>
-      </c>
-      <c r="D33" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920028</v>
-      </c>
-      <c r="B34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" t="s">
-        <v>151</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>22330051920332</v>
-      </c>
-      <c r="B35" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35" t="s">
-        <v>152</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6616,22 +5826,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920007</v>
+        <v>22330051920011</v>
       </c>
       <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6639,16 +5849,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920007</v>
+        <v>22330051920011</v>
       </c>
       <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
         <v>76</v>
       </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6662,19 +5872,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920321</v>
+        <v>22330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>59</v>
@@ -6685,22 +5895,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920321</v>
+        <v>22330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6708,22 +5918,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920003</v>
+        <v>22330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6731,22 +5941,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920006</v>
+        <v>22330051920321</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6754,22 +5964,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920011</v>
+        <v>22330051920021</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6777,16 +5987,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920017</v>
+        <v>22330051920021</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -6800,16 +6010,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920018</v>
+        <v>22330051920003</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -6823,16 +6033,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920021</v>
+        <v>22330051920006</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -6841,6 +6051,52 @@
         <v>58</v>
       </c>
       <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920017</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920018</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -197,6 +197,9 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
@@ -206,9 +209,6 @@
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Hernández Contreras Ángel</t>
   </si>
   <si>
@@ -224,73 +224,67 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
   </si>
   <si>
     <t>ROCETE</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
   </si>
   <si>
     <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
   </si>
 </sst>
 </file>
@@ -804,13 +798,13 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -881,13 +875,13 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -917,7 +911,7 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -958,13 +952,13 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -994,7 +988,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1035,13 +1029,13 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1112,13 +1106,13 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1154,7 +1148,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1189,13 +1183,13 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1225,7 +1219,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1266,13 +1260,13 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1302,7 +1296,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1343,13 +1337,13 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1420,13 +1414,13 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1456,7 +1450,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1497,13 +1491,13 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1533,13 +1527,13 @@
         <v>6</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>5</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1574,13 +1568,13 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1613,7 +1607,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1651,13 +1645,13 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1693,7 +1687,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1728,13 +1722,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1805,13 +1799,13 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1841,13 +1835,13 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>5</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -1882,13 +1876,13 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -1921,7 +1915,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -1959,13 +1953,13 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2001,7 +1995,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2036,13 +2030,13 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2072,7 +2066,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2113,13 +2107,13 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2149,13 +2143,13 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>5</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2190,13 +2184,13 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2226,13 +2220,13 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2267,13 +2261,13 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2344,13 +2338,13 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2421,13 +2415,13 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2498,13 +2492,13 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2575,13 +2569,13 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2611,7 +2605,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -2652,13 +2646,13 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2694,7 +2688,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2729,13 +2723,13 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2806,13 +2800,13 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2883,13 +2877,13 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -2960,13 +2954,13 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3002,7 +2996,7 @@
         <v>7</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3037,13 +3031,13 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3114,13 +3108,13 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3191,13 +3185,13 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3230,7 +3224,7 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3268,13 +3262,13 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3345,13 +3339,13 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3381,13 +3375,13 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>6</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -3532,13 +3526,13 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -3591,13 +3585,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -3650,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -3709,13 +3703,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -3768,13 +3762,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -3827,13 +3821,13 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -3886,13 +3880,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -3945,13 +3939,13 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -4004,13 +3998,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -4063,13 +4057,13 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -4122,13 +4116,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -4181,13 +4175,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -4240,13 +4234,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -4299,13 +4293,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -4358,13 +4352,13 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -4417,13 +4411,13 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -4476,13 +4470,13 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -4535,13 +4529,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -4594,13 +4588,13 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -4653,13 +4647,13 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -4712,13 +4706,13 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -4771,13 +4765,13 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -4830,13 +4824,13 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -4889,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -4948,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -5007,13 +5001,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -5066,13 +5060,13 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -5125,13 +5119,13 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -5184,13 +5178,13 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -5243,13 +5237,13 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -5302,13 +5296,13 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -5361,13 +5355,13 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -5420,13 +5414,13 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -5479,13 +5473,13 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -5595,7 +5589,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5616,7 +5610,7 @@
         <v>14.7</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5627,7 +5621,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -5636,19 +5630,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>88.2</v>
+        <v>85.3</v>
       </c>
       <c r="G4" s="2">
-        <v>11.8</v>
+        <v>14.7</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5659,7 +5653,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -5668,19 +5662,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="G5" s="2">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5691,7 +5685,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -5712,7 +5706,7 @@
         <v>5.9</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5794,7 +5788,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5826,19 +5820,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920011</v>
+        <v>22330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>59</v>
@@ -5849,16 +5843,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920011</v>
+        <v>22330051920006</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5872,22 +5866,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920007</v>
+        <v>22330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5895,16 +5889,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920007</v>
+        <v>22330051920015</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5918,19 +5912,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920321</v>
+        <v>22330051920021</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>60</v>
@@ -5941,22 +5935,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920321</v>
+        <v>22330051920021</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5964,22 +5958,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920021</v>
+        <v>22330051920003</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5987,13 +5981,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920021</v>
+        <v>22330051920017</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
         <v>86</v>
@@ -6010,13 +6004,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920003</v>
+        <v>22330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
         <v>87</v>
@@ -6033,70 +6027,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920006</v>
+        <v>22330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
         <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920017</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920018</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -206,12 +206,12 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Hernández Contreras Ángel</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Hernández Contreras Ángel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,9 +224,6 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -245,9 +242,6 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>QUERO</t>
   </si>
   <si>
@@ -264,9 +258,6 @@
   </si>
   <si>
     <t>ROCETE</t>
-  </si>
-  <si>
-    <t>EDER</t>
   </si>
   <si>
     <t>DIEGO JESUS</t>
@@ -807,7 +798,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -884,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -961,7 +952,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -997,7 +988,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1038,7 +1029,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1115,7 +1106,7 @@
         <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1192,7 +1183,7 @@
         <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1228,7 +1219,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1269,7 +1260,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1305,7 +1296,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1346,7 +1337,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1382,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1423,7 +1414,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1500,7 +1491,7 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1536,7 +1527,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1577,7 +1568,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1613,7 +1604,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1654,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1690,7 +1681,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1731,7 +1722,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1767,7 +1758,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1808,7 +1799,7 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1885,7 +1876,7 @@
         <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1921,7 +1912,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1962,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1998,7 +1989,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2039,7 +2030,7 @@
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2116,7 +2107,7 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2152,7 +2143,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2193,7 +2184,7 @@
         <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2229,7 +2220,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2270,7 +2261,7 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2347,7 +2338,7 @@
         <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2424,7 +2415,7 @@
         <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2460,7 +2451,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2501,7 +2492,7 @@
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2578,7 +2569,7 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2614,7 +2605,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2655,7 +2646,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2732,7 +2723,7 @@
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2768,7 +2759,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2809,7 +2800,7 @@
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2886,7 +2877,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2963,7 +2954,7 @@
         <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3040,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3117,7 +3108,7 @@
         <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3194,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3271,7 +3262,7 @@
         <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3348,7 +3339,7 @@
         <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3384,7 +3375,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3535,7 +3526,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3594,7 +3585,7 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3653,7 +3644,7 @@
         <v>95</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3712,7 +3703,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3771,7 +3762,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3830,7 +3821,7 @@
         <v>95</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3889,7 +3880,7 @@
         <v>75</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3948,7 +3939,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4007,7 +3998,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4066,7 +4057,7 @@
         <v>60</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4125,7 +4116,7 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4184,7 +4175,7 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4243,7 +4234,7 @@
         <v>95</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4302,7 +4293,7 @@
         <v>95</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4361,7 +4352,7 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4420,7 +4411,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4479,7 +4470,7 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4538,7 +4529,7 @@
         <v>95</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4597,7 +4588,7 @@
         <v>95</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4656,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4715,7 +4706,7 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>87.3</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4774,7 +4765,7 @@
         <v>90</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4833,7 +4824,7 @@
         <v>95</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4892,7 +4883,7 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4951,7 +4942,7 @@
         <v>95</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5010,7 +5001,7 @@
         <v>95</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5069,7 +5060,7 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5128,7 +5119,7 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5187,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5246,7 +5237,7 @@
         <v>95</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>87.3</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5305,7 +5296,7 @@
         <v>100</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5364,7 +5355,7 @@
         <v>100</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5423,7 +5414,7 @@
         <v>95</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>85.5</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -5482,7 +5473,7 @@
         <v>95</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -5685,7 +5676,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -5694,19 +5685,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="G6" s="2">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5717,7 +5708,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -5738,7 +5729,7 @@
         <v>5.9</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5788,7 +5779,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5820,22 +5811,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920006</v>
+        <v>22330051920015</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5843,16 +5834,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920006</v>
+        <v>22330051920015</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5866,22 +5857,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920015</v>
+        <v>22330051920021</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5889,16 +5880,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920015</v>
+        <v>22330051920021</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5912,22 +5903,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920021</v>
+        <v>22330051920003</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5935,16 +5926,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920021</v>
+        <v>22330051920017</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
         <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -5958,16 +5949,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920003</v>
+        <v>22330051920018</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
         <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -5981,70 +5972,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920017</v>
+        <v>22330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920018</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920321</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -197,15 +197,15 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Hernández Contreras Ángel</t>
   </si>
   <si>
@@ -227,9 +227,6 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -242,12 +239,12 @@
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>QUERO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -260,12 +257,12 @@
     <t>ROCETE</t>
   </si>
   <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
     <t>DANIEL</t>
   </si>
   <si>
@@ -276,6 +273,9 @@
   </si>
   <si>
     <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
   </si>
 </sst>
 </file>
@@ -786,7 +786,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -863,7 +863,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -940,7 +940,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1017,7 +1017,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -1094,7 +1094,7 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1130,7 +1130,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -1171,7 +1171,7 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1248,7 +1248,7 @@
         <v>4</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1284,7 +1284,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1325,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -1361,7 +1361,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1402,7 +1402,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1515,7 +1515,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1556,7 +1556,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>10</v>
@@ -1592,7 +1592,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1633,7 +1633,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1669,7 +1669,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1710,7 +1710,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>10</v>
@@ -1787,7 +1787,7 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -1864,7 +1864,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -1900,7 +1900,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -1941,7 +1941,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>9</v>
@@ -1977,7 +1977,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -2018,7 +2018,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -2095,7 +2095,7 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>10</v>
@@ -2131,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2172,7 +2172,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>9</v>
@@ -2249,7 +2249,7 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -2326,7 +2326,7 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -2362,7 +2362,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2403,7 +2403,7 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -2439,7 +2439,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -2480,7 +2480,7 @@
         <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>6</v>
@@ -2516,7 +2516,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -2557,7 +2557,7 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -2634,7 +2634,7 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>8</v>
@@ -2711,7 +2711,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -2747,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2788,7 +2788,7 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>10</v>
@@ -2865,7 +2865,7 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -2901,7 +2901,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -2942,7 +2942,7 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>8</v>
@@ -2978,7 +2978,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3019,7 +3019,7 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>8</v>
@@ -3055,7 +3055,7 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3096,7 +3096,7 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>10</v>
@@ -3132,7 +3132,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -3173,7 +3173,7 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J35">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3250,7 +3250,7 @@
         <v>4</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>6</v>
@@ -3327,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>8</v>
@@ -3363,7 +3363,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3514,7 +3514,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3573,7 +3573,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3632,7 +3632,7 @@
         <v>93.3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3691,7 +3691,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3750,7 +3750,7 @@
         <v>93.3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3809,7 +3809,7 @@
         <v>80</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3868,7 +3868,7 @@
         <v>46.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J10">
         <v>73.3</v>
@@ -3927,7 +3927,7 @@
         <v>93.3</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3986,7 +3986,7 @@
         <v>73.3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J12">
         <v>86.7</v>
@@ -4045,7 +4045,7 @@
         <v>46.7</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J13">
         <v>80</v>
@@ -4104,7 +4104,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -4163,7 +4163,7 @@
         <v>80</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4222,7 +4222,7 @@
         <v>93.3</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4281,7 +4281,7 @@
         <v>80</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4340,7 +4340,7 @@
         <v>93.3</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -4399,7 +4399,7 @@
         <v>93.3</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -4458,7 +4458,7 @@
         <v>93.3</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4517,7 +4517,7 @@
         <v>86.7</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4576,7 +4576,7 @@
         <v>93.3</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4635,7 +4635,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4694,7 +4694,7 @@
         <v>80</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4753,7 +4753,7 @@
         <v>80</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4812,7 +4812,7 @@
         <v>93.3</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4871,7 +4871,7 @@
         <v>93.3</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -4930,7 +4930,7 @@
         <v>80</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -4989,7 +4989,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5048,7 +5048,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5107,7 +5107,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -5166,7 +5166,7 @@
         <v>93.3</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J32">
         <v>100</v>
@@ -5225,7 +5225,7 @@
         <v>93.3</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5284,7 +5284,7 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J34">
         <v>100</v>
@@ -5343,7 +5343,7 @@
         <v>93.3</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
         <v>100</v>
@@ -5402,7 +5402,7 @@
         <v>80</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J36">
         <v>100</v>
@@ -5461,7 +5461,7 @@
         <v>80</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J37">
         <v>100</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5589,19 +5589,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>85.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>14.7</v>
+        <v>20.6</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -5633,7 +5633,7 @@
         <v>14.7</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -5653,19 +5653,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>88.2</v>
+        <v>85.3</v>
       </c>
       <c r="G5" s="2">
-        <v>11.8</v>
+        <v>14.7</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5779,7 +5779,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5826,7 +5826,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920021</v>
+        <v>22330051920003</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -5869,10 +5869,10 @@
         <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5880,16 +5880,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920021</v>
+        <v>22330051920017</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5903,16 +5903,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920003</v>
+        <v>22330051920018</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5926,22 +5926,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920017</v>
+        <v>22330051920321</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5949,47 +5949,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920018</v>
+        <v>22330051920382</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920321</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -3496,7 +3496,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -3520,31 +3520,31 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3555,7 +3555,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -3573,37 +3573,37 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3614,7 +3614,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -3629,16 +3629,16 @@
         <v>98.2</v>
       </c>
       <c r="H6">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I6">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>110</v>
+        <v>95.2</v>
       </c>
       <c r="L6">
         <v>95</v>
@@ -3647,22 +3647,22 @@
         <v>98.2</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3673,7 +3673,7 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -3697,7 +3697,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3706,22 +3706,22 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3732,7 +3732,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -3747,40 +3747,40 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I8">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>96.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3791,7 +3791,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -3806,40 +3806,40 @@
         <v>96.40000000000001</v>
       </c>
       <c r="H9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I9">
-        <v>95</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3850,7 +3850,7 @@
         <v>83.3</v>
       </c>
       <c r="C10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>86.7</v>
@@ -3865,40 +3865,40 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>46.7</v>
+        <v>65</v>
       </c>
       <c r="I10">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="J10">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="K10">
-        <v>30</v>
+        <v>42.9</v>
       </c>
       <c r="L10">
         <v>75</v>
       </c>
       <c r="M10">
+        <v>90</v>
+      </c>
+      <c r="N10">
+        <v>65</v>
+      </c>
+      <c r="O10">
+        <v>75</v>
+      </c>
+      <c r="P10">
         <v>80</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
       <c r="Q10">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3909,7 +3909,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -3924,16 +3924,16 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I11">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3942,22 +3942,22 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3968,7 +3968,7 @@
         <v>93.3</v>
       </c>
       <c r="C12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -3983,40 +3983,40 @@
         <v>90.90000000000001</v>
       </c>
       <c r="H12">
-        <v>73.3</v>
+        <v>83.3</v>
       </c>
       <c r="I12">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="J12">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K12">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>92.7</v>
+        <v>91.8</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4027,7 +4027,7 @@
         <v>93.3</v>
       </c>
       <c r="C13">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -4042,40 +4042,40 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H13">
-        <v>46.7</v>
+        <v>70</v>
       </c>
       <c r="I13">
-        <v>55</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J13">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K13">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="L13">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M13">
         <v>89.09999999999999</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4086,7 +4086,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -4104,13 +4104,13 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4119,22 +4119,22 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4145,7 +4145,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -4160,40 +4160,40 @@
         <v>92.7</v>
       </c>
       <c r="H15">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I15">
+        <v>93.2</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>95.2</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="N15">
         <v>90</v>
       </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
-      <c r="K15">
-        <v>110</v>
-      </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
-        <v>94.5</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
       <c r="O15">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4204,7 +4204,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -4219,40 +4219,40 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4263,7 +4263,7 @@
         <v>93.3</v>
       </c>
       <c r="C17">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -4278,40 +4278,40 @@
         <v>87.3</v>
       </c>
       <c r="H17">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="I17">
-        <v>55</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>90</v>
+        <v>76.2</v>
       </c>
       <c r="L17">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4322,7 +4322,7 @@
         <v>96.7</v>
       </c>
       <c r="C18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -4337,7 +4337,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -4346,7 +4346,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4355,22 +4355,22 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4381,7 +4381,7 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -4396,7 +4396,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4405,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4414,22 +4414,22 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4440,7 +4440,7 @@
         <v>96.7</v>
       </c>
       <c r="C20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -4455,40 +4455,40 @@
         <v>96.40000000000001</v>
       </c>
       <c r="H20">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="I20">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20">
-        <v>98.2</v>
+        <v>97.3</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4499,7 +4499,7 @@
         <v>96.7</v>
       </c>
       <c r="C21">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -4514,40 +4514,40 @@
         <v>90.90000000000001</v>
       </c>
       <c r="H21">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="I21">
-        <v>70</v>
+        <v>79.5</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="L21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M21">
-        <v>98.2</v>
+        <v>94.5</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4558,7 +4558,7 @@
         <v>93.3</v>
       </c>
       <c r="C22">
-        <v>85</v>
+        <v>70.8</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -4576,37 +4576,37 @@
         <v>93.3</v>
       </c>
       <c r="I22">
-        <v>50</v>
+        <v>61.4</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>90</v>
+        <v>76.2</v>
       </c>
       <c r="L22">
-        <v>95</v>
+        <v>82.5</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>61.4</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4617,7 +4617,7 @@
         <v>93.3</v>
       </c>
       <c r="C23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -4632,7 +4632,7 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -4641,7 +4641,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -4650,22 +4650,22 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4676,7 +4676,7 @@
         <v>96.7</v>
       </c>
       <c r="C24">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -4691,40 +4691,40 @@
         <v>94.5</v>
       </c>
       <c r="H24">
-        <v>80</v>
+        <v>88.3</v>
       </c>
       <c r="I24">
-        <v>55</v>
+        <v>77.3</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
-        <v>87.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>88.3</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -4750,40 +4750,40 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I25">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="L25">
+        <v>95</v>
+      </c>
+      <c r="M25">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="N25">
         <v>90</v>
       </c>
-      <c r="M25">
-        <v>98.2</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
       <c r="O25">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4794,7 +4794,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -4809,40 +4809,40 @@
         <v>98.2</v>
       </c>
       <c r="H26">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I26">
-        <v>85</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="L26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4853,7 +4853,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -4868,40 +4868,40 @@
         <v>94.5</v>
       </c>
       <c r="H27">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4912,7 +4912,7 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -4927,40 +4927,40 @@
         <v>98.2</v>
       </c>
       <c r="H28">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I28">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M28">
-        <v>89.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4971,7 +4971,7 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -4989,37 +4989,37 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>65</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L29">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M29">
         <v>98.2</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5030,7 +5030,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -5054,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5063,22 +5063,22 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5089,7 +5089,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -5113,7 +5113,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -5122,22 +5122,22 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5148,7 +5148,7 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -5163,40 +5163,40 @@
         <v>96.40000000000001</v>
       </c>
       <c r="H32">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I32">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>98.2</v>
+        <v>97.3</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5207,7 +5207,7 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="D33">
         <v>100</v>
@@ -5222,40 +5222,40 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H33">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I33">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M33">
-        <v>87.3</v>
+        <v>88.2</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5266,7 +5266,7 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -5284,37 +5284,37 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5325,7 +5325,7 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -5340,16 +5340,16 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I35">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5358,22 +5358,22 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5384,7 +5384,7 @@
         <v>80</v>
       </c>
       <c r="C36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -5402,37 +5402,37 @@
         <v>80</v>
       </c>
       <c r="I36">
-        <v>60</v>
+        <v>81.8</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>90</v>
+        <v>85.7</v>
       </c>
       <c r="L36">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="M36">
         <v>85.5</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5443,7 +5443,7 @@
         <v>100</v>
       </c>
       <c r="C37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -5458,40 +5458,40 @@
         <v>94.5</v>
       </c>
       <c r="H37">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I37">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L37">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M37">
-        <v>89.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -194,24 +194,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
+    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Hernández Contreras Ángel</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,7 +227,10 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>APALE</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>GUERRA</t>
@@ -239,13 +242,13 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>QUERO</t>
   </si>
   <si>
-    <t>TEXOCO</t>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>JERONIMO</t>
@@ -257,13 +260,13 @@
     <t>ROCETE</t>
   </si>
   <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
-    <t>DANIEL</t>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>LUIS</t>
@@ -273,9 +276,6 @@
   </si>
   <si>
     <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
   </si>
 </sst>
 </file>
@@ -801,22 +801,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -878,25 +878,25 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -955,22 +955,22 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -979,10 +979,10 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1032,22 +1032,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1109,25 +1109,25 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1136,7 +1136,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1186,22 +1186,22 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1210,16 +1210,16 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1263,22 +1263,22 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -1296,7 +1296,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1340,40 +1340,40 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>7</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1417,40 +1417,40 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>5</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1494,22 +1494,22 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>5</v>
@@ -1571,31 +1571,31 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1648,25 +1648,25 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1725,25 +1725,25 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -1752,13 +1752,13 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1802,25 +1802,25 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -1879,34 +1879,34 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>7</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -1956,40 +1956,40 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>7</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2033,25 +2033,25 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2110,40 +2110,40 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>7</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2187,40 +2187,40 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>5</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2264,22 +2264,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2341,31 +2341,31 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>5</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -2374,7 +2374,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2418,22 +2418,22 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>5</v>
@@ -2451,7 +2451,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2495,25 +2495,25 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2528,7 +2528,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2572,25 +2572,25 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2599,7 +2599,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2649,31 +2649,31 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>6</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2682,7 +2682,7 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2726,25 +2726,25 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -2803,22 +2803,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -2880,22 +2880,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2957,34 +2957,34 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>7</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3034,31 +3034,31 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>6</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3067,7 +3067,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3111,22 +3111,22 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3188,25 +3188,25 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3265,22 +3265,22 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3298,7 +3298,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3342,22 +3342,22 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3366,10 +3366,10 @@
         <v>6</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -3544,7 +3544,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3588,7 +3588,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O5">
         <v>95.5</v>
@@ -3597,13 +3597,13 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3647,7 +3647,7 @@
         <v>98.2</v>
       </c>
       <c r="N6">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O6">
         <v>84.09999999999999</v>
@@ -3656,13 +3656,13 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="R6">
         <v>95</v>
       </c>
       <c r="S6">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3765,7 +3765,7 @@
         <v>98.2</v>
       </c>
       <c r="N8">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O8">
         <v>95.5</v>
@@ -3774,13 +3774,13 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3824,7 +3824,7 @@
         <v>98.2</v>
       </c>
       <c r="N9">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O9">
         <v>84.09999999999999</v>
@@ -3833,13 +3833,13 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="R9">
         <v>97.5</v>
       </c>
       <c r="S9">
-        <v>98.2</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3883,22 +3883,22 @@
         <v>90</v>
       </c>
       <c r="N10">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="O10">
         <v>75</v>
       </c>
       <c r="P10">
-        <v>80</v>
+        <v>56.3</v>
       </c>
       <c r="Q10">
-        <v>42.9</v>
+        <v>28.1</v>
       </c>
       <c r="R10">
         <v>75</v>
       </c>
       <c r="S10">
-        <v>90</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3951,13 +3951,13 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4001,22 +4001,22 @@
         <v>91.8</v>
       </c>
       <c r="N12">
-        <v>83.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O12">
         <v>97.7</v>
       </c>
       <c r="P12">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="Q12">
-        <v>90.5</v>
+        <v>87.5</v>
       </c>
       <c r="R12">
         <v>100</v>
       </c>
       <c r="S12">
-        <v>91.8</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4060,22 +4060,22 @@
         <v>89.09999999999999</v>
       </c>
       <c r="N13">
-        <v>70</v>
+        <v>55.6</v>
       </c>
       <c r="O13">
         <v>65.90000000000001</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>62.5</v>
       </c>
       <c r="Q13">
-        <v>81</v>
+        <v>59.4</v>
       </c>
       <c r="R13">
         <v>70</v>
       </c>
       <c r="S13">
-        <v>89.09999999999999</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4119,7 +4119,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O14">
         <v>95.5</v>
@@ -4128,13 +4128,13 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4178,7 +4178,7 @@
         <v>93.59999999999999</v>
       </c>
       <c r="N15">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O15">
         <v>93.2</v>
@@ -4187,13 +4187,13 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>93.59999999999999</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4246,7 +4246,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R16">
         <v>97.5</v>
@@ -4296,7 +4296,7 @@
         <v>93.59999999999999</v>
       </c>
       <c r="N17">
-        <v>86.7</v>
+        <v>82.2</v>
       </c>
       <c r="O17">
         <v>65.90000000000001</v>
@@ -4305,13 +4305,13 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>76.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="R17">
         <v>87.5</v>
       </c>
       <c r="S17">
-        <v>93.59999999999999</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4355,7 +4355,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -4364,7 +4364,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4414,7 +4414,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4423,13 +4423,13 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R19">
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4473,7 +4473,7 @@
         <v>97.3</v>
       </c>
       <c r="N20">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O20">
         <v>93.2</v>
@@ -4482,13 +4482,13 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>95.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R20">
         <v>100</v>
       </c>
       <c r="S20">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4532,7 +4532,7 @@
         <v>94.5</v>
       </c>
       <c r="N21">
-        <v>91.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O21">
         <v>79.5</v>
@@ -4541,13 +4541,13 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>90.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R21">
         <v>97.5</v>
       </c>
       <c r="S21">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4591,7 +4591,7 @@
         <v>95.5</v>
       </c>
       <c r="N22">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="O22">
         <v>61.4</v>
@@ -4600,13 +4600,13 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>76.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R22">
         <v>82.5</v>
       </c>
       <c r="S22">
-        <v>95.5</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4650,7 +4650,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -4709,22 +4709,22 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N24">
-        <v>88.3</v>
+        <v>76.7</v>
       </c>
       <c r="O24">
         <v>77.3</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q24">
-        <v>95.2</v>
+        <v>87.5</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>90.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4768,7 +4768,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="N25">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O25">
         <v>90.90000000000001</v>
@@ -4777,13 +4777,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>95.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R25">
         <v>95</v>
       </c>
       <c r="S25">
-        <v>99.09999999999999</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4827,7 +4827,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="N26">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="O26">
         <v>90.90000000000001</v>
@@ -4836,13 +4836,13 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="R26">
         <v>97.5</v>
       </c>
       <c r="S26">
-        <v>99.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4886,7 +4886,7 @@
         <v>97.3</v>
       </c>
       <c r="N27">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O27">
         <v>90.90000000000001</v>
@@ -4895,13 +4895,13 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R27">
         <v>80</v>
       </c>
       <c r="S27">
-        <v>97.3</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4945,7 +4945,7 @@
         <v>93.59999999999999</v>
       </c>
       <c r="N28">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O28">
         <v>90.90000000000001</v>
@@ -4954,13 +4954,13 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R28">
         <v>97.5</v>
       </c>
       <c r="S28">
-        <v>93.59999999999999</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5004,7 +5004,7 @@
         <v>98.2</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O29">
         <v>84.09999999999999</v>
@@ -5013,13 +5013,13 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R29">
         <v>97.5</v>
       </c>
       <c r="S29">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5063,7 +5063,7 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -5078,7 +5078,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5122,7 +5122,7 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -5131,13 +5131,13 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R31">
         <v>100</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5181,7 +5181,7 @@
         <v>97.3</v>
       </c>
       <c r="N32">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O32">
         <v>90.90000000000001</v>
@@ -5190,13 +5190,13 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5240,7 +5240,7 @@
         <v>88.2</v>
       </c>
       <c r="N33">
-        <v>96.7</v>
+        <v>82.2</v>
       </c>
       <c r="O33">
         <v>88.59999999999999</v>
@@ -5249,13 +5249,13 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R33">
         <v>97.5</v>
       </c>
       <c r="S33">
-        <v>88.2</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5314,7 +5314,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5358,7 +5358,7 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O35">
         <v>97.7</v>
@@ -5417,22 +5417,22 @@
         <v>85.5</v>
       </c>
       <c r="N36">
-        <v>80</v>
+        <v>82.2</v>
       </c>
       <c r="O36">
         <v>81.8</v>
       </c>
       <c r="P36">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="Q36">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
       <c r="R36">
         <v>87.5</v>
       </c>
       <c r="S36">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5476,22 +5476,22 @@
         <v>91.8</v>
       </c>
       <c r="N37">
-        <v>90</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O37">
         <v>90.90000000000001</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R37">
         <v>97.5</v>
       </c>
       <c r="S37">
-        <v>91.8</v>
+        <v>91.5</v>
       </c>
     </row>
   </sheetData>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -5557,19 +5557,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>73.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>26.5</v>
+        <v>20.6</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5589,19 +5589,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>79.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>20.6</v>
+        <v>17.6</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -5633,7 +5633,7 @@
         <v>14.7</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -5653,19 +5653,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>85.3</v>
+        <v>91.2</v>
       </c>
       <c r="G5" s="2">
-        <v>14.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5676,7 +5676,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -5685,19 +5685,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -5729,7 +5729,7 @@
         <v>5.9</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5779,7 +5779,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5826,7 +5826,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5849,7 +5849,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920003</v>
+        <v>22330051920382</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -5869,10 +5869,10 @@
         <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5880,19 +5880,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920017</v>
+        <v>22330051920382</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>58</v>
@@ -5903,19 +5903,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920018</v>
+        <v>22330051920010</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
@@ -5926,22 +5926,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920321</v>
+        <v>22330051920017</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5949,24 +5949,47 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920382</v>
+        <v>22330051920018</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>59</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920321</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2AEM - Estadisticos 20222.xlsx
+++ b/grupos/2AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -203,12 +203,12 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Hernández Contreras Ángel</t>
   </si>
   <si>
@@ -224,58 +224,88 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>QUERO</t>
   </si>
   <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
     <t>ZARATE</t>
   </si>
   <si>
-    <t>COYOHUA</t>
+    <t>DIAZ</t>
   </si>
   <si>
     <t>JERONIMO</t>
   </si>
   <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
     <t>OSMAR UZIEL</t>
   </si>
   <si>
-    <t>DIEGO</t>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
   </si>
   <si>
     <t>LUIS</t>
   </si>
   <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
+    <t>VALENTINA</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER ANDRUS</t>
   </si>
 </sst>
 </file>
@@ -804,7 +834,7 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>9</v>
@@ -813,7 +843,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -881,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -890,7 +920,7 @@
         <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -899,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -958,7 +988,7 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -967,7 +997,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>8</v>
@@ -976,7 +1006,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1035,7 +1065,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>9</v>
@@ -1044,7 +1074,7 @@
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>10</v>
@@ -1112,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>7</v>
@@ -1121,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -1189,7 +1219,7 @@
         <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>7</v>
@@ -1198,7 +1228,7 @@
         <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>7</v>
@@ -1207,7 +1237,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1216,7 +1246,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1266,7 +1296,7 @@
         <v>3</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>5</v>
@@ -1275,7 +1305,7 @@
         <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -1284,7 +1314,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1293,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1343,7 +1373,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
         <v>7</v>
@@ -1352,7 +1382,7 @@
         <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>9</v>
@@ -1361,7 +1391,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1420,7 +1450,7 @@
         <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>7</v>
@@ -1429,7 +1459,7 @@
         <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -1447,7 +1477,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1497,7 +1527,7 @@
         <v>3</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -1506,7 +1536,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>5</v>
@@ -1574,7 +1604,7 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>8</v>
@@ -1583,7 +1613,7 @@
         <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>10</v>
@@ -1651,7 +1681,7 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -1660,7 +1690,7 @@
         <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>7</v>
@@ -1669,7 +1699,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1678,7 +1708,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1728,7 +1758,7 @@
         <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>9</v>
@@ -1737,7 +1767,7 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>9</v>
@@ -1755,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1805,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>7</v>
@@ -1814,7 +1844,7 @@
         <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>7</v>
@@ -1832,7 +1862,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -1882,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>8</v>
@@ -1891,7 +1921,7 @@
         <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -1959,7 +1989,7 @@
         <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>8</v>
@@ -1968,7 +1998,7 @@
         <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -1977,7 +2007,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2036,7 +2066,7 @@
         <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2045,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>7</v>
@@ -2054,7 +2084,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2063,7 +2093,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2113,7 +2143,7 @@
         <v>2</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -2122,7 +2152,7 @@
         <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -2131,7 +2161,7 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2190,7 +2220,7 @@
         <v>2</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>5</v>
@@ -2199,7 +2229,7 @@
         <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S22">
         <v>5</v>
@@ -2217,7 +2247,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2267,7 +2297,7 @@
         <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>9</v>
@@ -2276,7 +2306,7 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -2285,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2344,7 +2374,7 @@
         <v>3</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>6</v>
@@ -2353,7 +2383,7 @@
         <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>7</v>
@@ -2371,7 +2401,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2421,7 +2451,7 @@
         <v>4</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>6</v>
@@ -2430,7 +2460,7 @@
         <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>5</v>
@@ -2439,7 +2469,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -2498,7 +2528,7 @@
         <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -2507,7 +2537,7 @@
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>5</v>
@@ -2516,7 +2546,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -2525,7 +2555,7 @@
         <v>6</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2575,7 +2605,7 @@
         <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>7</v>
@@ -2584,7 +2614,7 @@
         <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>7</v>
@@ -2593,7 +2623,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2652,7 +2682,7 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>8</v>
@@ -2661,7 +2691,7 @@
         <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>7</v>
@@ -2670,7 +2700,7 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -2729,7 +2759,7 @@
         <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>8</v>
@@ -2738,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>10</v>
@@ -2747,7 +2777,7 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2806,7 +2836,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>10</v>
@@ -2815,7 +2845,7 @@
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>10</v>
@@ -2883,7 +2913,7 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>8</v>
@@ -2892,7 +2922,7 @@
         <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>10</v>
@@ -2960,7 +2990,7 @@
         <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>7</v>
@@ -2969,7 +2999,7 @@
         <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>10</v>
@@ -2978,7 +3008,7 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>8</v>
@@ -3037,7 +3067,7 @@
         <v>3</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>6</v>
@@ -3046,7 +3076,7 @@
         <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>5</v>
@@ -3064,7 +3094,7 @@
         <v>7</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3114,7 +3144,7 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>9</v>
@@ -3123,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>10</v>
@@ -3191,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>10</v>
@@ -3200,7 +3230,7 @@
         <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>10</v>
@@ -3268,7 +3298,7 @@
         <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>5</v>
@@ -3277,7 +3307,7 @@
         <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
         <v>9</v>
@@ -3345,7 +3375,7 @@
         <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>6</v>
@@ -3354,7 +3384,7 @@
         <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S37">
         <v>10</v>
@@ -3363,7 +3393,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -3372,7 +3402,7 @@
         <v>7</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -3591,7 +3621,7 @@
         <v>97.8</v>
       </c>
       <c r="O5">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3650,7 +3680,7 @@
         <v>97.8</v>
       </c>
       <c r="O6">
-        <v>84.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3659,7 +3689,7 @@
         <v>93.8</v>
       </c>
       <c r="R6">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S6">
         <v>98.3</v>
@@ -3718,7 +3748,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3768,7 +3798,7 @@
         <v>95.59999999999999</v>
       </c>
       <c r="O8">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3777,7 +3807,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S8">
         <v>97.7</v>
@@ -3827,7 +3857,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="O9">
-        <v>84.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3836,7 +3866,7 @@
         <v>93.8</v>
       </c>
       <c r="R9">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S9">
         <v>97.2</v>
@@ -3886,7 +3916,7 @@
         <v>50</v>
       </c>
       <c r="O10">
-        <v>75</v>
+        <v>53.1</v>
       </c>
       <c r="P10">
         <v>56.3</v>
@@ -3895,7 +3925,7 @@
         <v>28.1</v>
       </c>
       <c r="R10">
-        <v>75</v>
+        <v>48.4</v>
       </c>
       <c r="S10">
         <v>68.2</v>
@@ -3945,7 +3975,7 @@
         <v>96.7</v>
       </c>
       <c r="O11">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -4004,7 +4034,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="O12">
-        <v>97.7</v>
+        <v>92.2</v>
       </c>
       <c r="P12">
         <v>95.8</v>
@@ -4063,7 +4093,7 @@
         <v>55.6</v>
       </c>
       <c r="O13">
-        <v>65.90000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="P13">
         <v>62.5</v>
@@ -4072,7 +4102,7 @@
         <v>59.4</v>
       </c>
       <c r="R13">
-        <v>70</v>
+        <v>43.8</v>
       </c>
       <c r="S13">
         <v>79</v>
@@ -4122,7 +4152,7 @@
         <v>97.8</v>
       </c>
       <c r="O14">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4181,7 +4211,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="O15">
-        <v>93.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4190,7 +4220,7 @@
         <v>93.8</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="S15">
         <v>94.3</v>
@@ -4240,7 +4270,7 @@
         <v>96.7</v>
       </c>
       <c r="O16">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4249,7 +4279,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R16">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4299,7 +4329,7 @@
         <v>82.2</v>
       </c>
       <c r="O17">
-        <v>65.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4308,7 +4338,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="R17">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S17">
         <v>95.5</v>
@@ -4426,7 +4456,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S19">
         <v>99.40000000000001</v>
@@ -4476,7 +4506,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="O20">
-        <v>93.2</v>
+        <v>87.5</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4485,7 +4515,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="S20">
         <v>97.2</v>
@@ -4535,7 +4565,7 @@
         <v>75.59999999999999</v>
       </c>
       <c r="O21">
-        <v>79.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4544,7 +4574,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="R21">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S21">
         <v>93.8</v>
@@ -4594,7 +4624,7 @@
         <v>86.7</v>
       </c>
       <c r="O22">
-        <v>61.4</v>
+        <v>42.2</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4603,7 +4633,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="R22">
-        <v>82.5</v>
+        <v>54.7</v>
       </c>
       <c r="S22">
         <v>90.3</v>
@@ -4712,7 +4742,7 @@
         <v>76.7</v>
       </c>
       <c r="O24">
-        <v>77.3</v>
+        <v>81.3</v>
       </c>
       <c r="P24">
         <v>93.8</v>
@@ -4721,7 +4751,7 @@
         <v>87.5</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S24">
         <v>92.59999999999999</v>
@@ -4771,7 +4801,7 @@
         <v>80</v>
       </c>
       <c r="O25">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4780,7 +4810,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="R25">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S25">
         <v>97.7</v>
@@ -4830,7 +4860,7 @@
         <v>93.3</v>
       </c>
       <c r="O26">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4839,7 +4869,7 @@
         <v>93.8</v>
       </c>
       <c r="R26">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S26">
         <v>96.59999999999999</v>
@@ -4889,7 +4919,7 @@
         <v>95.59999999999999</v>
       </c>
       <c r="O27">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -4898,7 +4928,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R27">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S27">
         <v>95.5</v>
@@ -4948,7 +4978,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="O28">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -4957,7 +4987,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R28">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S28">
         <v>91.5</v>
@@ -5007,7 +5037,7 @@
         <v>97.8</v>
       </c>
       <c r="O29">
-        <v>84.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -5016,7 +5046,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R29">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S29">
         <v>98.3</v>
@@ -5184,7 +5214,7 @@
         <v>97.8</v>
       </c>
       <c r="O32">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -5243,7 +5273,7 @@
         <v>82.2</v>
       </c>
       <c r="O33">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5252,7 +5282,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R33">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S33">
         <v>91.5</v>
@@ -5302,7 +5332,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5361,7 +5391,7 @@
         <v>95.59999999999999</v>
       </c>
       <c r="O35">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -5420,7 +5450,7 @@
         <v>82.2</v>
       </c>
       <c r="O36">
-        <v>81.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P36">
         <v>95.8</v>
@@ -5429,7 +5459,7 @@
         <v>87.5</v>
       </c>
       <c r="R36">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S36">
         <v>85.8</v>
@@ -5479,7 +5509,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="O37">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P37">
         <v>95.8</v>
@@ -5488,7 +5518,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R37">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S37">
         <v>91.5</v>
@@ -5557,19 +5587,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>79.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>20.6</v>
+        <v>32.4</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5644,7 +5674,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -5653,19 +5683,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>91.2</v>
+        <v>85.3</v>
       </c>
       <c r="G5" s="2">
-        <v>8.800000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5676,7 +5706,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -5685,19 +5715,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>94.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="G6" s="2">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5779,7 +5809,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5811,16 +5841,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920015</v>
+        <v>22330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5834,22 +5864,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920015</v>
+        <v>22330051920010</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5857,22 +5887,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920382</v>
+        <v>22330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5880,22 +5910,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920382</v>
+        <v>22330051920015</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5903,22 +5933,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920010</v>
+        <v>22330051920018</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5926,22 +5956,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920017</v>
+        <v>22330051920018</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5949,22 +5979,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920018</v>
+        <v>22330051920321</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5975,21 +6005,205 @@
         <v>22330051920321</v>
       </c>
       <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920382</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920382</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920021</v>
+      </c>
+      <c r="B12" t="s">
         <v>73</v>
       </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920021</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920013</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920017</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920023</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
         <v>85</v>
       </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
         <v>58</v>
       </c>
-      <c r="G9">
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920332</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>
